--- a/Caffeine Intake Analysis.xlsx
+++ b/Caffeine Intake Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA211\DataSets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B43A93A-7665-4D91-B4DC-904CADD0D737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1648B6B5-0A81-4056-AB67-439183E07C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="2240" windowWidth="21600" windowHeight="12670" xr2:uid="{E82878B6-37ED-4C51-936C-93B403B8F964}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{E82878B6-37ED-4C51-936C-93B403B8F964}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
   <si>
     <t>DATE</t>
   </si>
@@ -52,12 +52,15 @@
   <si>
     <t>Caffeine Intake (mg)</t>
   </si>
+  <si>
+    <t>Observation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,50 +68,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF356854"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F8F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -116,156 +85,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF356854"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -281,6 +107,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{072C90B9-FD47-40B7-BECC-7F1989B54E4C}" name="Table2" displayName="Table2" ref="A1:D23" totalsRowShown="0">
+  <autoFilter ref="A1:D23" xr:uid="{072C90B9-FD47-40B7-BECC-7F1989B54E4C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4D34D5F9-A211-4B49-8F83-803B4998DE29}" name="Observation"/>
+    <tableColumn id="2" xr3:uid="{4CB8E2D7-6C6F-4DA0-AD25-FEA3625C4BDF}" name="DATE"/>
+    <tableColumn id="3" xr3:uid="{E951D7EF-64A0-4465-957F-AA05A514029A}" name="Caffeine Intake (mg)"/>
+    <tableColumn id="4" xr3:uid="{7D691CD0-2A24-444E-86C1-07E3FE0ECA59}" name="Day Type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,268 +439,353 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9171C7-D024-4269-9FF2-181EB23463AD}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="4" width="10.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
         <v>46114</v>
       </c>
-      <c r="B2" s="4">
+      <c r="C2">
         <v>350</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6">
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
         <v>46115</v>
       </c>
-      <c r="B3" s="7">
+      <c r="C3">
         <v>425</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
         <v>46116</v>
       </c>
-      <c r="B4" s="4">
+      <c r="C4">
         <v>270</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
         <v>46117</v>
       </c>
-      <c r="B5" s="7">
+      <c r="C5">
         <v>400</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
         <v>46118</v>
       </c>
-      <c r="B6" s="4">
+      <c r="C6">
         <v>350</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6">
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
         <v>46119</v>
       </c>
-      <c r="B7" s="7">
+      <c r="C7">
         <v>454</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
         <v>46120</v>
       </c>
-      <c r="B8" s="4">
+      <c r="C8">
         <v>250</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6">
+      <c r="D8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
         <v>46121</v>
       </c>
-      <c r="B9" s="7">
+      <c r="C9">
         <v>280</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+      <c r="D9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
         <v>46122</v>
       </c>
-      <c r="B10" s="4">
+      <c r="C10">
         <v>250</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
         <v>46123</v>
       </c>
-      <c r="B11" s="7">
+      <c r="C11">
         <v>134</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
         <v>46124</v>
       </c>
-      <c r="B12" s="4">
+      <c r="C12">
         <v>334</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
         <v>46125</v>
       </c>
-      <c r="B13" s="7">
+      <c r="C13">
         <v>450</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
         <v>46126</v>
       </c>
-      <c r="B14" s="4">
+      <c r="C14">
         <v>300</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6">
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
         <v>46127</v>
       </c>
-      <c r="B15" s="7">
+      <c r="C15">
         <v>300</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
         <v>46128</v>
       </c>
-      <c r="B16" s="4">
+      <c r="C16">
         <v>150</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="6">
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
         <v>46129</v>
       </c>
-      <c r="B17" s="7">
+      <c r="C17">
         <v>150</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
         <v>46130</v>
       </c>
-      <c r="B18" s="4">
+      <c r="C18">
         <v>300</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
         <v>46131</v>
       </c>
-      <c r="B19" s="7">
+      <c r="C19">
         <v>300</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
         <v>46132</v>
       </c>
-      <c r="B20" s="9">
+      <c r="C20">
         <v>34</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6">
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
         <v>46133</v>
       </c>
-      <c r="B21" s="10">
+      <c r="C21">
         <v>150</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3">
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
         <v>46134</v>
       </c>
-      <c r="B22" s="9">
+      <c r="C22">
         <v>150</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="11">
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
         <v>46135</v>
       </c>
-      <c r="B23" s="12">
+      <c r="C23">
         <v>300</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -870,7 +794,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB0C856ABD89BE41939A1BC4FE8E4EB6" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fdbfa22bb12883f12f06401da683a41a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe52d7f82ece3aca8c4482d35c4ac573" ns3:_="">
     <xsd:import namespace="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a"/>
@@ -1026,15 +950,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30281A57-E328-4476-BBED-7D68221433BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BBBEE2E-D1A0-4E47-92B6-E2A7F989EA2E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1042,7 +974,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD8FA76-8A54-4D11-B978-D77A78C74064}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1058,20 +990,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30281A57-E328-4476-BBED-7D68221433BA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="b9b8594a-3bf1-4574-8aab-2fb9178ddd6a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>